--- a/output/full_scan/batch_seq5_2026-06-23.xlsx
+++ b/output/full_scan/batch_seq5_2026-06-23.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O147"/>
+  <dimension ref="A1:O149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.19630413028594</v>
+        <v>66.19630411604373</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>22.32427104536092</v>
+        <v>22.3242712359028</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.620405774032999</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0127066513380799</v>
+        <v>0.0127066514514126</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>73.24698397881895</v>
+        <v>73.24698398110691</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>46.32307333578972</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4310015198548882</v>
+        <v>0.4310015198342887</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>73.64326210051766</v>
+        <v>73.64326211584932</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>29.22717308559789</v>
+        <v>29.22717304992737</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.974932769895178</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2761677405583454</v>
+        <v>0.2761677405748309</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.86404127404779</v>
+        <v>68.86404127786882</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>47.79716223537192</v>
+        <v>47.79716222701284</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.109918737631894</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.08693929411449371</v>
+        <v>0.08693929408358329</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>71.06264364060863</v>
+        <v>71.06264362402956</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>38.24474425353554</v>
+        <v>38.24474422645438</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>3.992027299922171</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.705517441409168</v>
+        <v>1.705517441697646</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>62.12820019860578</v>
+        <v>62.1282002753515</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>14.71398718236497</v>
+        <v>14.71398724206498</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>3.947457449018388</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.5591961002950926</v>
+        <v>0.5591960999447739</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>89.77460606144049</v>
+        <v>89.77460596395169</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>36.52851425332005</v>
+        <v>36.52851435539288</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>2.143698292199116</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.648911553406263</v>
+        <v>1.648911553323839</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>74.84609703439388</v>
+        <v>74.84609702991776</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>37.34598134881083</v>
+        <v>37.34598135203709</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>3.217772836644791</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>2.557769657978826</v>
+        <v>2.557769658071551</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>59.04428943589067</v>
+        <v>59.04428949849076</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>24.14790285805572</v>
+        <v>24.14790287215905</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.103984573650377</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.7181958729681123</v>
+        <v>0.7181958723499491</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>68.15669184764037</v>
+        <v>68.15669184210185</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>35.01327628482044</v>
+        <v>35.01327626868107</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>2.512901084011673</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.216907886871758</v>
+        <v>0.2169078868099436</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>76.45440417001444</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>16.0110909063742</v>
+        <v>16.01109095689558</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>6.281708549088793</v>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>62.25268095814761</v>
+        <v>62.25268097504285</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>34.94338899346639</v>
+        <v>34.94338905665538</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.438691135018404</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.0009616852361715</v>
+        <v>0.000961685199079</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1163,21 +1163,21 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4952</v>
+        <v>5251</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>凌通</t>
+          <t>天鉞電</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>852.3155425662809</v>
+        <v>842.7692277200123</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>58</v>
+        <v>31.4</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>59.72558266055979</v>
+        <v>58.77582319753738</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>28.36936134820555</v>
+        <v>29.37597206938795</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.9681782738106576</v>
+        <v>0.5761900286592836</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.7162065294965516</v>
+        <v>0.02469382749158</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5251</v>
+        <v>4939</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>天鉞電</t>
+          <t>亞電</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>842.7692277200611</v>
+        <v>839.7088379340604</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>31.4</v>
+        <v>60</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.77582287393089</v>
+        <v>56.89657327782619</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>29.37597201953428</v>
+        <v>35.98903994953798</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5761900286592836</v>
+        <v>0.2730960314401612</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0246938283158089</v>
+        <v>-0.4155124083067463</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4939</v>
+        <v>4952</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>亞電</t>
+          <t>凌通</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>839.7088379340604</v>
+        <v>832.3155425662809</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.89657327688067</v>
+        <v>59.72558269902959</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>35.98903994953798</v>
+        <v>28.36936132018131</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.2730960314401612</v>
+        <v>0.9681782738106576</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.4155124083067463</v>
+        <v>0.7162065293626172</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>58.31396179653201</v>
+        <v>58.31396185011739</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>29.05630990873442</v>
+        <v>29.05630979907077</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.4558459313171988</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.3107590048282169</v>
+        <v>-0.3107590049312421</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.48242644914552</v>
+        <v>60.48242649396273</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>39.6112339588512</v>
+        <v>39.61123413485993</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.8903714532228517</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.7045273145331508</v>
+        <v>0.7045273142755821</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1428,21 +1428,21 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4989</v>
+        <v>5351</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>榮科</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>826.331801698664</v>
+        <v>824.2477978679715</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>54.46872403601537</v>
+        <v>55.24143540879045</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21.81772001436061</v>
+        <v>20.69987807806545</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.55143783954302</v>
+        <v>1.176651687078252</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.5204634607524468</v>
+        <v>0.3106163244983344</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5351</v>
+        <v>4968</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>鈺創</t>
+          <t>立積</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>824.2477978679715</v>
+        <v>819.3666736877318</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>55.24143542159848</v>
+        <v>58.32541847450462</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20.69987809382722</v>
+        <v>15.47259754279278</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.176651687078252</v>
+        <v>1.888313087737202</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3106163244365181</v>
+        <v>0.8847780560771297</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5289</v>
+        <v>5536</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>819.476447913372</v>
+        <v>815.8104838332119</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1885</v>
+        <v>1260</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,25 +1559,25 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>55.03805798385901</v>
+        <v>65.04338903739597</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>24.03866512604354</v>
+        <v>32.92901085393596</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6189984985757727</v>
+        <v>0.5619806967388237</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-9.938380124859536</v>
+        <v>11.71479917950914</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4968</v>
+        <v>5426</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>立積</t>
+          <t>振發</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>819.3666736877319</v>
+        <v>812.3498424319702</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.32541828037632</v>
+        <v>71.70097192334472</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15.47259750305978</v>
+        <v>45.65230024089693</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.888313087737202</v>
+        <v>0.716358576248907</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.8847780573134756</v>
+        <v>0.6758153674389176</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5471</v>
+        <v>4989</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>松翰</t>
+          <t>榮科</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>817.5748273971838</v>
+        <v>811.331801698664</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>62.4</v>
+        <v>94</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>67.3525944561143</v>
+        <v>54.46872404600205</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>36.56224632301166</v>
+        <v>21.81771997497813</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.46844541391182</v>
+        <v>1.55143783954302</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.9558807299776944</v>
+        <v>0.520463460639121</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5536</v>
+        <v>5245</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>聖暉*</t>
+          <t>智晶</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>815.8104838332118</v>
+        <v>803.5456729507047</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1260</v>
+        <v>28.05</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>65.04338901824022</v>
+        <v>61.46385903980548</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>32.92901083151664</v>
+        <v>29.06185797697521</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5619806967388237</v>
+        <v>1.675210567049451</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>11.71479918167286</v>
+        <v>-0.0058697363321514</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5245</v>
+        <v>5471</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>智晶</t>
+          <t>松翰</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>803.545672950705</v>
+        <v>802.5748273971838</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>28.05</v>
+        <v>62.4</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>61.46385898568359</v>
+        <v>67.35259447155155</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>29.06185799445285</v>
+        <v>36.56224633611376</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.675210567049451</v>
+        <v>1.46844541391182</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,11 +1789,11 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.005869736280638</v>
+        <v>0.9558807298952688</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>68.7099218347434</v>
+        <v>68.70992185232028</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>40.55607850713113</v>
+        <v>40.55607847455656</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.5668570359435778</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.117621332330689</v>
+        <v>1.117621332258565</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>61.0152739564086</v>
+        <v>61.01527398544525</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>32.34938065294309</v>
+        <v>32.3493805164053</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.8230629475892346</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.164384043957309</v>
+        <v>-1.164384043689423</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>788.1557927609182</v>
+        <v>788.155792760918</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>18505</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.44805691831267</v>
+        <v>55.44805692784688</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.99489038661616</v>
+        <v>19.99489039051781</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.7938693819232145</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>15.62378904580339</v>
+        <v>15.62378905404637</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>786.1886166630119</v>
+        <v>786.1886166630118</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>491.5</v>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>62.75552217228791</v>
+        <v>62.7555221933908</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24.24597740083233</v>
+        <v>24.24597735548428</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1.08400987376958</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.935592931392432</v>
+        <v>1.93559293118646</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>785.7684404090783</v>
+        <v>785.7684404090784</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>42.75</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>52.72649185128677</v>
+        <v>52.72649193617495</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>18.79208196736014</v>
+        <v>18.79208194502219</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>3.133518852837856</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0280336672187901</v>
+        <v>0.0280336671775744</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>48.98702786670658</v>
+        <v>48.98702787937062</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>21.84527412105927</v>
+        <v>21.84527409828235</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1.941016646460646</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-2.836392931341604</v>
+        <v>-2.836392931609489</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>762.5509061017764</v>
+        <v>752.5509061017765</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>17.95</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>56.54951826464908</v>
+        <v>56.54951833316706</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16.19437552822394</v>
+        <v>16.1943756247104</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.741533651836783</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.10238633017968</v>
+        <v>0.1023863301178652</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>61.22538307250816</v>
+        <v>61.22538313092081</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>37.27391632792004</v>
+        <v>37.27391632116961</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>2.602999909842289</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.2348795079151129</v>
+        <v>0.2348795077708843</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>744.2246639234286</v>
+        <v>734.2246639234286</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>174.5</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.5764021559944</v>
+        <v>55.57640208500908</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>19.41897632070951</v>
+        <v>19.41897659743506</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>2.144034759288669</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.5315650121855544</v>
+        <v>0.5315650133188945</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>62.32409168831211</v>
+        <v>62.32409172455826</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>29.30428040089414</v>
+        <v>29.30428041404036</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.9856400196318228</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.3308604395549515</v>
+        <v>0.3308604395034376</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>59.9932259337267</v>
+        <v>59.99322593610693</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>31.36478677253828</v>
+        <v>31.36478671388134</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>1.432313874955035</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>2.484806689827565</v>
+        <v>2.484806689951142</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>67.96873093570775</v>
+        <v>67.96873095007425</v>
       </c>
       <c r="I37" s="2" t="n">
         <v>30.33104758333321</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4123358856438663</v>
+        <v>0.4123358856232619</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5483</v>
+        <v>5289</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>700.8205131224558</v>
+        <v>704.476447913372</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>173.5</v>
+        <v>1885</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>58.28548346983748</v>
+        <v>55.03805799247857</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>28.98289881775093</v>
+        <v>24.03866513095141</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.556801076978524</v>
+        <v>0.6189984985757727</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.569074884089409</v>
+        <v>-9.938380126302119</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>4919</v>
+        <v>5483</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>699.8790027901128</v>
+        <v>700.8205131224558</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>194.5</v>
+        <v>173.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,29 +2513,29 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>53.99052648328956</v>
+        <v>58.28548348469334</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>24.20373237923749</v>
+        <v>28.98289874417877</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.212927400194484</v>
+        <v>0.556801076978524</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.4105529499264859</v>
+        <v>1.569074883780315</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>55.87524593041242</v>
+        <v>55.87524597088046</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>35.95388907265223</v>
+        <v>35.95388905891879</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.5944357727551977</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.2262609490762994</v>
+        <v>-0.2262609489938678</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>62.18104484322219</v>
+        <v>62.18104481098656</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>36.57751026338987</v>
+        <v>36.57751038306697</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>2.506486313888241</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.1430308868968648</v>
+        <v>0.1430308869792878</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>5228</v>
+        <v>4919</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>鈺鎧</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>678.5728953779968</v>
+        <v>684.8790027901128</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>64.3</v>
+        <v>194.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.64276899777775</v>
+        <v>53.99052648410692</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>49.37652926184475</v>
+        <v>24.20373236988858</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6313435542152854</v>
+        <v>2.212927400194484</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.348803632311897</v>
+        <v>0.4105529499470837</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>5353</v>
+        <v>5228</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>台林</t>
+          <t>鈺鎧</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>678.3420864290557</v>
+        <v>678.5728953779968</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>31.55</v>
+        <v>64.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>56.12247743334576</v>
+        <v>51.64276899869039</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>58.61780349921816</v>
+        <v>49.37652921912911</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.2955917879163129</v>
+        <v>0.6313435542152854</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.2476753039652477</v>
+        <v>-1.3488036323222</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>5347</v>
+        <v>5353</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>台林</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>667.8033265325812</v>
+        <v>678.3420864290557</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>186.5</v>
+        <v>31.55</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>61.55032984414191</v>
+        <v>56.12247747483745</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>15.44704750197936</v>
+        <v>58.61780349474501</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.984877169624631</v>
+        <v>0.2955917879163129</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1.858048420630036</v>
+        <v>-0.2476753040064589</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>5381</v>
+        <v>5347</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>光譜</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>664.0435037460288</v>
+        <v>667.8033265325812</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>28.2</v>
+        <v>186.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,49 +2831,49 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>50.46005712950952</v>
+        <v>61.55032985519352</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>28.47999175045703</v>
+        <v>15.44704753187796</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4056514105582883</v>
+        <v>1.984877169624631</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.3792506976288621</v>
+        <v>1.858048420382753</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6155</v>
+        <v>5381</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>鈞寶</t>
+          <t>光譜</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>655.6578352190886</v>
+        <v>664.0435037460288</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>88.5</v>
+        <v>28.2</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>62.28652591628912</v>
+        <v>50.46005719528552</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>54.24705539434942</v>
+        <v>28.47999168670248</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4845871003987454</v>
+        <v>0.4056514105582883</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,11 +2902,11 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.889352617532829</v>
+        <v>-0.3792506977433052</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.55411243220354</v>
+        <v>49.55411243774262</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>30.23475611806674</v>
+        <v>30.23475617248493</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1.470606096835112</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.654777479936877</v>
+        <v>1.654777479885364</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>644.8800228060522</v>
+        <v>644.8800228060524</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>81.59999999999999</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>55.06266372406642</v>
+        <v>55.06266501896662</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.90739810525046</v>
+        <v>23.90739864199601</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.750864911342356</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0408812890284079</v>
+        <v>-0.0408812895123481</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>57.33400298090976</v>
+        <v>57.33400312309176</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>17.52032497154924</v>
+        <v>17.52032498411162</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>1.380130070774614</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.483747687457958</v>
+        <v>0.4837476866337318</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>61.70418713151338</v>
+        <v>61.7041871879315</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>27.01693155378989</v>
+        <v>27.01693147468176</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.9095438535784394</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0278026823024556</v>
+        <v>-0.027802682337485</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.56986413303593</v>
+        <v>48.56986419877578</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>27.60435315786198</v>
+        <v>27.60435310925267</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.4123905833979142</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.8522717588945348</v>
+        <v>-0.8522717596157419</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3177,21 +3177,21 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6103</v>
+        <v>6155</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>合邦</t>
+          <t>鈞寶</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>629.6390470253406</v>
+        <v>630.6578352190886</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>32</v>
+        <v>88.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.47136622664023</v>
+        <v>62.2865259215091</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>7.902641451791752</v>
+        <v>54.24705539434942</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.524122057382466</v>
+        <v>0.4845871003987454</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>1.545667314436927</v>
+        <v>0.8893526174916122</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>5269</v>
+        <v>6103</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>合邦</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>622.1353452669306</v>
+        <v>629.6390470253406</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1425</v>
+        <v>32</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,49 +3255,49 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.14922388011183</v>
+        <v>51.47136622664023</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16.94082001335263</v>
+        <v>7.902641390878648</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5851723360922472</v>
+        <v>1.524122057382466</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-6.530997179078399</v>
+        <v>1.545667314323594</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>5460</v>
+        <v>5269</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>同協</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>615.8663252699149</v>
+        <v>622.1353452669306</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>15.45</v>
+        <v>1425</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>53.32464980924191</v>
+        <v>50.14922405961572</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>28.53894337887142</v>
+        <v>16.94082001335264</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.8959548153014826</v>
+        <v>0.5851723360922472</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.08867903060389939</v>
+        <v>-6.530997184229616</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>5475</v>
+        <v>5460</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>德宏</t>
+          <t>同協</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>615.8107491056606</v>
+        <v>615.8663252699145</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>279</v>
+        <v>15.45</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.84020793259244</v>
+        <v>53.32464993130623</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.11244302392408</v>
+        <v>28.53894308058603</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8504857385788716</v>
+        <v>0.8959548153014826</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>2.303053214281237</v>
+        <v>0.08867903057299049</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>5344</v>
+        <v>5475</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>立衛</t>
+          <t>德宏</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>614.6907567044177</v>
+        <v>615.8107491056606</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>16.55</v>
+        <v>279</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>55.67233935796298</v>
+        <v>51.84020793468707</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16.15556861266813</v>
+        <v>20.11244302892642</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.863580167981612</v>
+        <v>0.8504857385788716</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0788682523284242</v>
+        <v>2.303053214260654</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>5432</v>
+        <v>5344</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>新門</t>
+          <t>立衛</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>613.7153963307887</v>
+        <v>614.6907567044177</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>153</v>
+        <v>16.55</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>61.05056357515411</v>
+        <v>55.67233934001381</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.51211714199505</v>
+        <v>16.15556862439962</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.781540236501169</v>
+        <v>2.863580167981612</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>2.548102923561947</v>
+        <v>0.0788682523593333</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4973</v>
+        <v>5432</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>廣穎</t>
+          <t>新門</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>591.3745587354671</v>
+        <v>613.7153963307892</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>60.81572511222755</v>
+        <v>61.05056361949552</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46.63777742106571</v>
+        <v>21.51211715838307</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7212563626443961</v>
+        <v>1.781540236501169</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.636628748613127</v>
+        <v>2.548102923046776</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>5481</v>
+        <v>4973</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>新華</t>
+          <t>廣穎</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>573.6386033037262</v>
+        <v>591.3745587354671</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>21.65</v>
+        <v>183</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>60.96978148763</v>
+        <v>60.81572511934328</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>33.7663755977842</v>
+        <v>46.63777741348936</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6934806790262054</v>
+        <v>0.7212563626443961</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,51 +3591,51 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.4262428037506617</v>
+        <v>-1.63662874874705</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>4945</v>
+        <v>5481</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>陞達科技</t>
+          <t>新華</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>550.5710737637258</v>
+        <v>573.6386033037261</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>21.65</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>54.07464430494792</v>
+        <v>60.96981187396882</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12.78813456213036</v>
+        <v>33.76647326134208</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4265127663271301</v>
+        <v>0.6934806790262054</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,51 +3644,51 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.5464948707817345</v>
+        <v>0.4262427454163297</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>4995</v>
+        <v>4945</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>晶達</t>
+          <t>陞達科技</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>550.5553274340475</v>
+        <v>550.5710737637257</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>45.75</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="G61" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.93597958735349</v>
+        <v>54.12165061846808</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.35388066669859</v>
+        <v>12.79503624125492</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4725379724495009</v>
+        <v>0.4265127663271301</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.1012481148204697</v>
+        <v>0.5461465656107363</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6139</v>
+        <v>4995</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>晶達</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>549.8223654723236</v>
+        <v>550.5553274340475</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>791</v>
+        <v>45.75</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.26714402290055</v>
+        <v>52.9359793532858</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>22.14280165266261</v>
+        <v>21.35388066908961</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6009922210096598</v>
+        <v>0.4725379724495009</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,11 +3750,11 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.709157437304953</v>
+        <v>-0.1012481148410783</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>58.75530830657387</v>
+        <v>58.7553083889876</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.29805632917753</v>
+        <v>23.29805627473871</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.9094089313147152</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1310739163848752</v>
+        <v>0.1310739163457233</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.1499855879343</v>
+        <v>47.14998562934411</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>17.17822715811144</v>
+        <v>17.17822718277043</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.4088101001443772</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.8332148947441151</v>
+        <v>-0.8332148949089548</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.35698499122586</v>
+        <v>52.35698510504734</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>9.445459150841543</v>
+        <v>9.445459163760267</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.6900697174709729</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1247862935435305</v>
+        <v>0.124786293584743</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>538.0761399135826</v>
+        <v>538.0761399135824</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>43.35</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.1244308622385</v>
+        <v>50.12443087640619</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>10.3585797423151</v>
+        <v>10.35857963706888</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.6514701795995884</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.2723390731496893</v>
+        <v>-0.2723390731702937</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3972,21 +3972,21 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>5356</v>
+        <v>6139</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>協益</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>534.4867421069154</v>
+        <v>534.8223654723212</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>27.5</v>
+        <v>791</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.9725016623604</v>
+        <v>52.2671440464049</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>28.24408755210279</v>
+        <v>22.14280167042934</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6861216586993947</v>
+        <v>0.6009922210096598</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0322436957064821</v>
+        <v>-1.709157438335303</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>5484</v>
+        <v>5356</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>慧友</t>
+          <t>協益</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>532.0560357680927</v>
+        <v>534.4867421069154</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>45.5</v>
+        <v>27.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.9660473431116</v>
+        <v>51.97250175718376</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>34.28019089853597</v>
+        <v>28.24408746275457</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3975525617858746</v>
+        <v>0.6861216586993947</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.155475888932582</v>
+        <v>-0.0322436957476928</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>4915</v>
+        <v>5484</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>慧友</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>529.3258636324165</v>
+        <v>532.0560357680927</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>75.2</v>
+        <v>45.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.56244278797105</v>
+        <v>44.96604737589442</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.2198495115308</v>
+        <v>34.28019082884474</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8896170848274803</v>
+        <v>0.3975525617858746</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1185962434505459</v>
+        <v>-1.15547588921077</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>5457</v>
+        <v>4915</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>宣德</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>525.1796694008896</v>
+        <v>529.3258636324165</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>36</v>
+        <v>75.2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,49 +4156,49 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>57.37074248924795</v>
+        <v>50.56244293929965</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>24.86299023347321</v>
+        <v>13.21984951276684</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7049949651717902</v>
+        <v>0.8896170848274803</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.7234390978132211</v>
+        <v>-0.1185962436772063</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>4760</v>
+        <v>5457</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>勤凱</t>
+          <t>宣德</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>520.7666622226639</v>
+        <v>525.1796694008896</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>349.5</v>
+        <v>36</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46.67998596315213</v>
+        <v>57.37074260425922</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.83392411958627</v>
+        <v>24.86299024345148</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8689918442381466</v>
+        <v>0.7049949651717902</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-9.443952868318677</v>
+        <v>0.7234390975556487</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>5487</v>
+        <v>4760</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>通泰</t>
+          <t>勤凱</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>511.2745332436344</v>
+        <v>520.7666622226639</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>28.65</v>
+        <v>349.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>55.11912114177766</v>
+        <v>46.67998598682278</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>29.46689446686039</v>
+        <v>21.83392418674207</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.8084961938164756</v>
+        <v>0.8689918442381466</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1601043751777604</v>
+        <v>-9.443952868833804</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>5292</v>
+        <v>5487</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>華懋</t>
+          <t>通泰</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>510.0159667178938</v>
+        <v>511.2745332436344</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>226</v>
+        <v>28.65</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.12918445960882</v>
+        <v>55.11912119596054</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.45988629716914</v>
+        <v>29.466894471795</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.3628582338881839</v>
+        <v>0.8084961938164756</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>1.704597780430965</v>
+        <v>0.1601043751262479</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>4906</v>
+        <v>5292</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>華懋</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>504.2603774928306</v>
+        <v>510.0159667178938</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>44.5</v>
+        <v>226</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.43593093498122</v>
+        <v>53.12918447694221</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25.66183241882691</v>
+        <v>15.45988629482491</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.8197168899507998</v>
+        <v>0.3628582338881839</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.4175180876533215</v>
+        <v>1.704597780533969</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>4916</v>
+        <v>4906</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>事欣科</t>
+          <t>正文</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>501.4663587114693</v>
+        <v>504.2603774928306</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>100</v>
+        <v>44.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.76640941428642</v>
+        <v>51.43593093953634</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>34.3970987356285</v>
+        <v>25.66183247767359</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.955923671864952</v>
+        <v>0.8197168899507998</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-3.167435607899215</v>
+        <v>-0.4175180877048337</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>4972</v>
+        <v>4916</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>湯石照明</t>
+          <t>事欣科</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>495.0713111112303</v>
+        <v>501.4663587114693</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>16.9</v>
+        <v>100</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>60.79337969177954</v>
+        <v>49.76640943552695</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>27.40935400224387</v>
+        <v>34.3970987433765</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3793375088012476</v>
+        <v>0.955923671864952</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0367949643403731</v>
+        <v>-3.167435608043463</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>4554</v>
+        <v>4972</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>橙的</t>
+          <t>湯石照明</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>494.664885757995</v>
+        <v>495.0713111112302</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>30.2</v>
+        <v>16.9</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.02407065156225</v>
+        <v>60.79338014602455</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>21.09104046517773</v>
+        <v>27.40935406885844</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7700684222944155</v>
+        <v>0.3793375088012476</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0128465427318545</v>
+        <v>0.0367949642785539</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>5222</v>
+        <v>4554</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>全訊</t>
+          <t>橙的</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>486.0409536219615</v>
+        <v>494.664885757995</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>119.5</v>
+        <v>30.2</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,49 +4580,49 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>48.09657859457555</v>
+        <v>49.02407074553707</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.22269814401092</v>
+        <v>21.09104047322446</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.585829080263188</v>
+        <v>0.7700684222944155</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.7141396505106155</v>
+        <v>-0.0128465428348865</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>5314</v>
+        <v>5222</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>世紀*</t>
+          <t>全訊</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>483.0417140759968</v>
+        <v>486.0409536219615</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>60.5</v>
+        <v>119.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,49 +4633,49 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.95444607831801</v>
+        <v>48.09657871155934</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>6.142339777084142</v>
+        <v>22.22269818558702</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.33532187211543</v>
+        <v>1.585829080263188</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.4393170560622117</v>
+        <v>0.7141396500984998</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>5205</v>
+        <v>5314</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>中茂</t>
+          <t>世紀*</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>473.4025126807491</v>
+        <v>483.0417140759968</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>23.25</v>
+        <v>60.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.55143010548552</v>
+        <v>47.95444621898921</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>17.31586169708714</v>
+        <v>6.142339776437823</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2.589149882443715</v>
+        <v>1.33532187211543</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0335695700649725</v>
+        <v>0.4393170558561574</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>4977</v>
+        <v>5205</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>眾達-KY</t>
+          <t>中茂</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>461.1234025430613</v>
+        <v>473.4025126807491</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>185.5</v>
+        <v>23.25</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46.3579135072365</v>
+        <v>47.55143024873751</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>9.514181207969218</v>
+        <v>17.3158616715351</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6645797714867872</v>
+        <v>2.589149882443715</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.6039489083421152</v>
+        <v>0.0335695701370931</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>5272</v>
+        <v>4977</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>笙科</t>
+          <t>眾達-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>449.3166927027486</v>
+        <v>471.1234025430613</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>21.75</v>
+        <v>185.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>48.00265602162211</v>
+        <v>46.35791352068134</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.05038157118907</v>
+        <v>9.5141812085879</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6846431710173632</v>
+        <v>0.6645797714867872</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0816899256839652</v>
+        <v>-0.6039489086718186</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>5215</v>
+        <v>5272</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>科嘉-KY</t>
+          <t>笙科</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>442.6568273113745</v>
+        <v>449.3166927027486</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>44.75</v>
+        <v>21.75</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>50.61840507895293</v>
+        <v>48.00265605415289</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>29.11571278276131</v>
+        <v>13.05038158254526</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.2832081302087016</v>
+        <v>0.6846431710173632</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.3753220805701356</v>
+        <v>0.081689925704571</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6120</v>
+        <v>5215</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>達運</t>
+          <t>科嘉-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>431.558703266441</v>
+        <v>442.6568273113745</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>14.5</v>
+        <v>44.75</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>52.22327400076629</v>
+        <v>50.61840510358509</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.30629818099815</v>
+        <v>29.11571270123413</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8276025540880934</v>
+        <v>0.2832081302087016</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0168171563133134</v>
+        <v>-0.3753220805289265</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>4967</v>
+        <v>5498</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>凱崴</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>427.8292185933658</v>
+        <v>423.29716223398</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>272</v>
+        <v>65</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>47.56431932829054</v>
+        <v>48.09203366372526</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16.70785888699126</v>
+        <v>14.05258098011251</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6287188122935069</v>
+        <v>0.6328134566265778</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-1.430227898096797</v>
+        <v>0.4743841059787078</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>5469</v>
+        <v>6120</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>瀚宇博</t>
+          <t>達運</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>425.5183173185735</v>
+        <v>421.5587032664411</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>86.8</v>
+        <v>14.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>53.31784537970032</v>
+        <v>52.22327407038911</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15.20826677753544</v>
+        <v>16.30629813304613</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.352996619556538</v>
+        <v>0.8276025540880934</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.6247090256027475</v>
+        <v>0.0168171562250259</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>5498</v>
+        <v>5493</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>凱崴</t>
+          <t>三聯</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>423.29716223398</v>
+        <v>419.1709720393349</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.09203366057211</v>
+        <v>46.90572162495192</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>14.05258099519461</v>
+        <v>19.94741692315198</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6328134566265778</v>
+        <v>0.3932412441655381</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.4743841059869523</v>
+        <v>-0.6428449373438753</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>5493</v>
+        <v>5469</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>三聯</t>
+          <t>瀚宇博</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>419.1709720393349</v>
+        <v>415.5183173185735</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>90</v>
+        <v>86.8</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.90572155658137</v>
+        <v>53.3178454152191</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19.94741696283858</v>
+        <v>15.20826676467464</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3932412441655381</v>
+        <v>1.352996619556538</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,11 +5128,11 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.6428449368493286</v>
+        <v>0.6247090254997232</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>49.1001425924662</v>
+        <v>49.10014264281425</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>25.46396653355066</v>
+        <v>25.46396655468769</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>1.235223853221256</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.196900413662246</v>
+        <v>-0.196900413754969</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>411.8698453569861</v>
+        <v>411.8698453569862</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>96</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>48.39172995015781</v>
+        <v>48.39172996696503</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15.92481093625004</v>
+        <v>15.92481091240399</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>1.995868319460194</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.8669880701508852</v>
+        <v>0.8669880701920949</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>50.87226516103085</v>
+        <v>50.87226517355089</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.949687051535</v>
+        <v>18.94968702363727</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.5307012916393254</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-6.750264763569781</v>
+        <v>-6.750264763858219</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>54.75078036675145</v>
+        <v>54.75078036369984</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>21.39768766747749</v>
+        <v>21.3976876908495</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.547005677282389</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.8410251255831711</v>
+        <v>0.8410251256449917</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46.13010650620178</v>
+        <v>46.13010661298184</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>10.8751968558726</v>
+        <v>10.87519691526078</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.4240346617014699</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.07627687913911579</v>
+        <v>0.0762768787270021</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>42.92892455670179</v>
+        <v>42.9289248189457</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>13.24450546825976</v>
+        <v>13.24450554571397</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>1.766609750503326</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0115786390036075</v>
+        <v>0.0115786389314866</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>400.8161476236479</v>
+        <v>400.8161476236478</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>28.2</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45.05536873455356</v>
+        <v>45.05536899074648</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>21.64464183973137</v>
+        <v>21.64464185748482</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.8277983032299675</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.120916632379723</v>
+        <v>-0.1209166322148723</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6141</v>
+        <v>4967</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>柏承</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>391.2115011950817</v>
+        <v>392.8292185933658</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>35.25</v>
+        <v>272</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>50.56352925319157</v>
+        <v>47.56431934553849</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.22448091092453</v>
+        <v>16.70785893413346</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4057424679773282</v>
+        <v>0.6287188122935069</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.4402375018275816</v>
+        <v>-1.430227898323429</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>4935</v>
+        <v>6141</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>茂林-KY</t>
+          <t>柏承</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>383.3332351139638</v>
+        <v>391.2115011950817</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>38.75</v>
+        <v>35.25</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>49.11730257612822</v>
+        <v>50.563529259345</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20.43977631865798</v>
+        <v>17.22448092398672</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.782252691979169</v>
+        <v>0.4057424679773282</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0703499500518419</v>
+        <v>-0.4402375018605485</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>5225</v>
+        <v>4935</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>茂林-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>381.6013615153659</v>
+        <v>383.3332351139638</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>73</v>
+        <v>38.75</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>48.33437476722943</v>
+        <v>49.11730263392877</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>21.27658922482446</v>
+        <v>20.43977634350453</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4192582801469091</v>
+        <v>0.782252691979169</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.2704112687050332</v>
+        <v>-0.0703499500312354</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>4585</v>
+        <v>5225</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>達明</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>380.961229512428</v>
+        <v>381.601361515366</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>310.5</v>
+        <v>73</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>42.47742805996364</v>
+        <v>48.33437463355354</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.46989944189711</v>
+        <v>21.27658957897223</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4199266260647066</v>
+        <v>0.4192582801469091</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-2.736477699541192</v>
+        <v>0.2704112695498698</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>5291</v>
+        <v>4585</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>邑昇</t>
+          <t>達明</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>369.7356698331558</v>
+        <v>380.961229512428</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>62.7</v>
+        <v>310.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>40.93013869379077</v>
+        <v>42.47742815613519</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20.81749703138121</v>
+        <v>20.46989944189711</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5517948072171256</v>
+        <v>0.4199266260647066</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.5600028238879481</v>
+        <v>-2.736477703765374</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>5315</v>
+        <v>6125</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>光聯</t>
+          <t>廣運</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>368.0804821796576</v>
+        <v>370.2311249344622</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>23.05</v>
+        <v>60.8</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>56.43325951952817</v>
+        <v>47.18072156475503</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.57740252058963</v>
+        <v>21.31096224572861</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.9439327181030788</v>
+        <v>0.5125531366797647</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.1061124777556164</v>
+        <v>-0.5035291218940761</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6124</v>
+        <v>5291</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>業強</t>
+          <t>邑昇</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>366.0091372832949</v>
+        <v>369.7356698331558</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>30.35</v>
+        <v>62.7</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>47.71954494215847</v>
+        <v>40.93013871490327</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>23.6298047658697</v>
+        <v>20.81749700358224</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.2832193203160308</v>
+        <v>0.5517948072171256</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.2120726674518136</v>
+        <v>-0.5600028238879481</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>4938</v>
+        <v>5315</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>光聯</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>362.5795913356111</v>
+        <v>368.0804821796576</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>23.05</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>37.48421410637077</v>
+        <v>56.43325952777437</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>22.611440273755</v>
+        <v>17.57740247792558</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5169491030074019</v>
+        <v>0.9439327181030788</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-1.785613071595301</v>
+        <v>0.1061124777659181</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6112</v>
+        <v>6124</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>邁達特</t>
+          <t>業強</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>358.3490422407081</v>
+        <v>366.0091372832949</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>44.35</v>
+        <v>30.35</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>43.42340377738822</v>
+        <v>47.71954497849915</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.65918838358373</v>
+        <v>23.62980474667189</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3203609158072187</v>
+        <v>0.2832193203160308</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.3717905208876352</v>
+        <v>-0.2120726674518136</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6114</v>
+        <v>4938</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>久威</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>356.7825587955129</v>
+        <v>362.5795913356111</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>30</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.99291544665069</v>
+        <v>37.48421421097868</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>26.71904605152285</v>
+        <v>22.61144033155916</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.551680976315738</v>
+        <v>0.5169491030074019</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0149040547125905</v>
+        <v>-1.78561307182198</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>5220</v>
+        <v>6112</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>萬達光電</t>
+          <t>邁達特</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>355.2427796478629</v>
+        <v>358.3490422407081</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>21.25</v>
+        <v>44.35</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>44.00274262939898</v>
+        <v>43.42340383157853</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>24.86371678792871</v>
+        <v>16.65918858898559</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.7411743144267131</v>
+        <v>0.3203609158072187</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1544708989603885</v>
+        <v>-0.3717905212997532</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6152</v>
+        <v>6114</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>百一</t>
+          <t>久威</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>350.7666421720814</v>
+        <v>356.7825587955129</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>13.8</v>
+        <v>30</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>37.28376464991286</v>
+        <v>48.99291572241939</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.167445075363981</v>
+        <v>26.71904606061313</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.082071654796368</v>
+        <v>0.551680976315738</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1158437354978135</v>
+        <v>0.0149040546816835</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>4912</v>
+        <v>5220</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>聯德控股-KY</t>
+          <t>萬達光電</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>346.9953165009794</v>
+        <v>355.2427796478629</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>88.09999999999999</v>
+        <v>21.25</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>40.30492887210476</v>
+        <v>44.00274265669783</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>20.75657431032822</v>
+        <v>24.86371678519936</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3165276139685684</v>
+        <v>0.7411743144267131</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-1.218471966210838</v>
+        <v>-0.1544708989397818</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>4903</v>
+        <v>6152</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>百一</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>341.5959039526217</v>
+        <v>350.7666421720814</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>39</v>
+        <v>13.8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>37.8121629164385</v>
+        <v>37.28376472771035</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.87646311629572</v>
+        <v>9.167445065513792</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.192564144136325</v>
+        <v>1.082071654796368</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.1821275121270595</v>
+        <v>-0.1158437355349034</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6115</v>
+        <v>4912</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>鎰勝</t>
+          <t>聯德控股-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>340.5286985607253</v>
+        <v>346.9953165009794</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>48.15</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>49.16236166109022</v>
+        <v>40.3049289616021</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>11.74355905510432</v>
+        <v>20.7565742901171</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.685184842372893</v>
+        <v>0.3165276139685684</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0575171950682584</v>
+        <v>-1.218471966313875</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>5278</v>
+        <v>4903</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>尚凡</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>325.1694724608726</v>
+        <v>341.5959039526217</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>23.65</v>
+        <v>39</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>48.01435850551884</v>
+        <v>37.81216300243257</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.76632945925739</v>
+        <v>15.87646318666362</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6549732194894924</v>
+        <v>1.192564144136325</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0220454153448632</v>
+        <v>-0.182127512384628</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>5438</v>
+        <v>6115</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>東友</t>
+          <t>鎰勝</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>325.1656514323916</v>
+        <v>340.5286985607253</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>19.05</v>
+        <v>48.15</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>48.11531622229683</v>
+        <v>49.16236174814546</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>21.75838716540295</v>
+        <v>11.74355907815518</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.8661214359721914</v>
+        <v>0.685184842372893</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0002495370123569</v>
+        <v>-0.0575171951506772</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>5348</v>
+        <v>5278</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>正能量智能</t>
+          <t>尚凡</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>323.2883913088974</v>
+        <v>325.1694724608726</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>39.42200492179092</v>
+        <v>48.01435846973347</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.76340301670485</v>
+        <v>17.76632947555438</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.0638320507819426</v>
+        <v>0.6549732194894924</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.98567711292669</v>
+        <v>0.022045415416982</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>5203</v>
+        <v>5438</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>東友</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>318.5765768063326</v>
+        <v>325.1656514323916</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>19.05</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>50.18791376234195</v>
+        <v>48.11531636779423</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19.75753159072173</v>
+        <v>21.75838717949893</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5418678398214046</v>
+        <v>0.8661214359721914</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.21904852462186</v>
+        <v>-0.0002495371050813</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>4949</v>
+        <v>5348</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>有成精密</t>
+          <t>正能量智能</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>317.0725637000376</v>
+        <v>323.288391308897</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>87.8</v>
+        <v>0</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.40777155888892</v>
+        <v>39.42200491154313</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>17.61224700847175</v>
+        <v>12.76340297533575</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4454899913624799</v>
+        <v>0.0638320507819426</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-1.07673631169266</v>
+        <v>-0.9856771128648728</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>4951</v>
+        <v>5203</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>精拓科</t>
+          <t>訊連</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>312.5475166571867</v>
+        <v>318.5765768063325</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>100</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>40.71988263748593</v>
+        <v>50.18791433875358</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>28.9403004913435</v>
+        <v>19.75753159635983</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.6416774023501061</v>
+        <v>0.5418678398214046</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-1.780434086574883</v>
+        <v>-0.2190485258169949</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>5258</v>
+        <v>4949</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>虹堡</t>
+          <t>有成精密</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>307.0606117772242</v>
+        <v>317.0725637000377</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>50</v>
+        <v>87.8</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46.03638057962257</v>
+        <v>44.4077715125178</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.30714765698703</v>
+        <v>17.61224711475522</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.6212765876832718</v>
+        <v>0.4454899913624799</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0303796798315452</v>
+        <v>-1.076736311507219</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>5243</v>
+        <v>4951</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>精拓科</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>300.6457407820919</v>
+        <v>312.5475166571867</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>41.48588864449138</v>
+        <v>40.71988266058764</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13.7941074354724</v>
+        <v>28.9403004853446</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.589528918658891</v>
+        <v>0.6416774023501061</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-1.60652125787768</v>
+        <v>-1.780434086883973</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>4582</v>
+        <v>5243</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>聚恆-創</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>289.7242441841919</v>
+        <v>300.6457407820919</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>25.5</v>
+        <v>103</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>42.10110319112496</v>
+        <v>41.48588867072213</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>12.64519416632843</v>
+        <v>13.79410740132553</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.2980162687371379</v>
+        <v>0.589528918658891</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.2765452291386714</v>
+        <v>-1.606521258073444</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>5439</v>
+        <v>5258</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>虹堡</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>284.6324407185201</v>
+        <v>297.0606117772242</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>321.5</v>
+        <v>50</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>36.58730289791495</v>
+        <v>46.03638075655821</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>19.46660006097012</v>
+        <v>15.30714769247216</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.6485423537014592</v>
+        <v>0.6212765876832718</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-3.455233779203077</v>
+        <v>-0.0303796803672944</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>5443</v>
+        <v>4582</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>均豪</t>
+          <t>聚恆-創</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>282.6122138292109</v>
+        <v>289.7242441841919</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>107</v>
+        <v>25.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>43.33047631340029</v>
+        <v>42.10110332922332</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>20.03146096776114</v>
+        <v>12.64519437963241</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.5511891181923422</v>
+        <v>0.2980162687371379</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.2172934086653937</v>
+        <v>0.2765452290356445</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>4749</v>
+        <v>5439</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>新應材</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>280.3732615575324</v>
+        <v>284.6324407185201</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>917</v>
+        <v>321.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>40.93762839227773</v>
+        <v>36.58730297344044</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>15.36871701642821</v>
+        <v>19.46660004628661</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.397345801657106</v>
+        <v>0.6485423537014592</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-6.724259213836476</v>
+        <v>-3.455233779512133</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>4588</v>
+        <v>5443</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>玖鼎電力</t>
+          <t>均豪</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>274.4663996642301</v>
+        <v>282.6122138292109</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>59.8</v>
+        <v>107</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>54.30733026423937</v>
+        <v>43.33047634400617</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>19.57051283542437</v>
+        <v>20.03146093320591</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.3275645994181774</v>
+        <v>0.5511891181923422</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.1761707750905538</v>
+        <v>-0.2172934090569107</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>5287</v>
+        <v>4749</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>數字</t>
+          <t>新應材</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>272.5777451004241</v>
+        <v>280.3732615575324</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>148</v>
+        <v>917</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>46.16115685225483</v>
+        <v>40.93762844088886</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>16.62075431146698</v>
+        <v>15.36871693553049</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.5545639521943473</v>
+        <v>1.397345801657106</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.5517385988014338</v>
+        <v>-6.724259215072866</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>4979</v>
+        <v>5287</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>數字</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>271.4567097013965</v>
+        <v>272.5777451004241</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>525</v>
+        <v>148</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>44.47695532651078</v>
+        <v>46.16115699646109</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>13.50536143411842</v>
+        <v>16.62075431976714</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.092554544539293</v>
+        <v>0.5545639521943473</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>1</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-3.386923112015974</v>
+        <v>0.5517385985953605</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6108</v>
+        <v>4979</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>競國</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>270.2971361921538</v>
+        <v>271.4567097013958</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>18.9</v>
+        <v>525</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>47.35992002102795</v>
+        <v>44.47695533499315</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.59522479714795</v>
+        <v>13.5053614215993</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.6995452512660872</v>
+        <v>1.092554544539293</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0356842081577133</v>
+        <v>-3.386923112840289</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>4966</v>
+        <v>6108</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>競國</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>269.5494251988687</v>
+        <v>270.2971361921538</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>661</v>
+        <v>18.9</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>42.45055703801771</v>
+        <v>47.35992006095756</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>18.04283078671018</v>
+        <v>11.59522480565507</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.6974464810703883</v>
+        <v>0.6995452512660872</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-11.24729866362809</v>
+        <v>-0.0356842081989259</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>5234</v>
+        <v>4966</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>達興材料</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>264.9222551208128</v>
+        <v>269.5494251988687</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>385</v>
+        <v>661</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,16 +7230,16 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>43.4506030747747</v>
+        <v>42.45055704065598</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>15.59886642985553</v>
+        <v>18.04283082932515</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.6894009588640185</v>
+        <v>0.6974464810703883</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0344749735854064</v>
+        <v>-11.24729866259776</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>6123</v>
+        <v>5234</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>上奇</t>
+          <t>達興材料</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>255.8005641221031</v>
+        <v>264.9222551208121</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>42.25</v>
+        <v>385</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>33.83720276440449</v>
+        <v>43.45060310840815</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>19.53087464984909</v>
+        <v>15.59886641837569</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.7800564122103109</v>
+        <v>0.6894009588640185</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.4606991374060638</v>
+        <v>-0.0344749736884519</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>4927</v>
+        <v>4588</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>泰鼎-KY</t>
+          <t>玖鼎電力</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>255.6482051446215</v>
+        <v>264.4663996642301</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>48.9</v>
+        <v>59.8</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>44.0396938175975</v>
+        <v>54.30733053214006</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>14.15488951357248</v>
+        <v>19.57051277336766</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.8467760222665355</v>
+        <v>0.3275645994181774</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.3176258823108026</v>
+        <v>0.1761707751935893</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>4933</v>
+        <v>6123</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>上奇</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>253.30116874906</v>
+        <v>255.8005641221031</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>67.5</v>
+        <v>42.25</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>44.42992851682173</v>
+        <v>33.8372028942396</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>19.61509957983365</v>
+        <v>19.53087465423943</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.3629569671889312</v>
+        <v>0.7800564122103109</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.6753109840273245</v>
+        <v>-0.4606991375915138</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>4960</v>
+        <v>4933</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>246.44703703631</v>
+        <v>253.30116874906</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>28.25</v>
+        <v>67.5</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>37.75824209709514</v>
+        <v>44.42992838571379</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>16.47428701121061</v>
+        <v>19.61509974893918</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.7724043205133961</v>
+        <v>0.3629569671889312</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.2179799740808534</v>
+        <v>-0.6753109834297477</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>4971</v>
+        <v>4960</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>IET-KY</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>243.893755423454</v>
+        <v>246.44703703631</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>540</v>
+        <v>28.25</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>38.65144551891848</v>
+        <v>37.7582421031141</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>16.95892736708266</v>
+        <v>16.47428700896123</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1.056310236725993</v>
+        <v>0.7724043205133961</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-6.458017872416001</v>
+        <v>-0.2179799741117576</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7523,21 +7523,21 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>6133</v>
+        <v>4971</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>金橋</t>
+          <t>IET-KY</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>242.7434678033675</v>
+        <v>243.893755423453</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>22.9</v>
+        <v>540</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>47.06795823180793</v>
+        <v>38.65144552829809</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>11.82830071612752</v>
+        <v>16.95892737837366</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.5151560342644669</v>
+        <v>1.056310236725993</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.09219555162279081</v>
+        <v>-6.458017873508105</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>5388</v>
+        <v>6133</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>中磊</t>
+          <t>金橋</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>240.077583552261</v>
+        <v>242.7434678033675</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>79.90000000000001</v>
+        <v>22.9</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>40.47164541241485</v>
+        <v>47.06795831523012</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>14.82498507349508</v>
+        <v>11.82830072124378</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.8714155104255495</v>
+        <v>0.5151560342644669</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.8802171709616667</v>
+        <v>-0.09219555165369769</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>6117</v>
+        <v>4927</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>迎廣</t>
+          <t>泰鼎-KY</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>232.002469076073</v>
+        <v>240.6482051446215</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>48.9</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>39.60203871580203</v>
+        <v>44.03969383167417</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>19.77246162950301</v>
+        <v>14.15488947770714</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.4472727323063851</v>
+        <v>0.8467760222665355</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>0</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.6633298188871111</v>
+        <v>-0.3176258823108026</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7682,21 +7682,21 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>5355</v>
+        <v>5388</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>佳總</t>
+          <t>中磊</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>229.0242738921734</v>
+        <v>240.077583552261</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>6.36</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>41.09427331982754</v>
+        <v>40.47164534228409</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>18.33306371603271</v>
+        <v>14.82498510371049</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.7467785818014271</v>
+        <v>0.8714155104255495</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.0161675356155664</v>
+        <v>-0.8802171712707512</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>6128</v>
+        <v>6117</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>上福</t>
+          <t>迎廣</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>226.9894689713408</v>
+        <v>232.002469076073</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>20.4</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,16 +7760,16 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>49.21912818573514</v>
+        <v>39.60203879876162</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>26.32782520061245</v>
+        <v>19.772461639436</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.5543778007380352</v>
+        <v>0.4472727323063851</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.029868457499609</v>
+        <v>-0.6633298193198289</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>4909</v>
+        <v>5355</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>新復興</t>
+          <t>佳總</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>210.5429375709644</v>
+        <v>229.0242738921734</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>48.05</v>
+        <v>6.36</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>37.60995551831776</v>
+        <v>41.09427333238376</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>27.03853910722191</v>
+        <v>18.33306374808144</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.9758855836744924</v>
+        <v>0.7467785818014271</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.06976401598718859</v>
+        <v>-0.0161675356155664</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>6136</v>
+        <v>6128</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>富爾特</t>
+          <t>上福</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>193.4270098886923</v>
+        <v>226.9894689713408</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>25.15</v>
+        <v>20.4</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>45.82034019054093</v>
+        <v>49.21912828097205</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>11.54510111904734</v>
+        <v>26.32782519067972</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.5038232334030295</v>
+        <v>0.5543778007380352</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.0737749758477466</v>
+        <v>0.029868457499609</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>5223</v>
+        <v>4909</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>安力-KY</t>
+          <t>新復興</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>182.3681205403932</v>
+        <v>210.5429375709653</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>25.4</v>
+        <v>48.05</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>48.96659369214923</v>
+        <v>37.60995568667016</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>11.86504052813296</v>
+        <v>27.03853909178355</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>1.073866014458298</v>
+        <v>0.9758855836744924</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-0.0038359562713331</v>
+        <v>0.06976401551325261</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>4905</v>
+        <v>6136</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>台聯電</t>
+          <t>富爾特</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>171.7351659697365</v>
+        <v>193.4270098886923</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>70.7</v>
+        <v>25.15</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>38.20884158811495</v>
+        <v>45.82034024098648</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>17.62369779079129</v>
+        <v>11.54510143415513</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.2992865728290924</v>
+        <v>0.5038232334030295</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.6399342495582223</v>
+        <v>-0.0737749759713832</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>6118</v>
+        <v>5223</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>建達</t>
+          <t>安力-KY</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>160.5141778197957</v>
+        <v>182.3681205403931</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>17.45</v>
+        <v>25.4</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>49.00418561612461</v>
+        <v>48.96659384688699</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>18.79341585652957</v>
+        <v>11.86504053475319</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.7714776743086131</v>
+        <v>1.073866014458298</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.0099135278215464</v>
+        <v>-0.0038359564052701</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8053,18 +8053,18 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>4974</v>
+        <v>4905</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>亞泰</t>
+          <t>台聯電</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>157.6892828823565</v>
+        <v>171.7351659697365</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>70.7</v>
@@ -8078,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>35.46333237585215</v>
+        <v>38.20884163406699</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>19.8570790929415</v>
+        <v>17.62369779079129</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.9738237986275606</v>
+        <v>0.2992865728290924</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.7165675353371428</v>
+        <v>-0.63993424957883</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>4999</v>
+        <v>6118</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>鑫禾</t>
+          <t>建達</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>153.5185540640375</v>
+        <v>160.5141778197957</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>20.75</v>
+        <v>17.45</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>50.4672050305004</v>
+        <v>49.0041855494099</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>18.45052972271922</v>
+        <v>18.79341584442432</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.8622952530138016</v>
+        <v>0.7714776743086131</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>0.0155610007013171</v>
+        <v>0.009913527934878499</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>4942</v>
+        <v>4974</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>嘉彰</t>
+          <t>亞泰</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>121.229643274381</v>
+        <v>157.6892828823565</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>37.4</v>
+        <v>70.7</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>44.10257837256528</v>
+        <v>35.46333249766874</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>14.25181969737796</v>
+        <v>19.85707916712312</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>1.143923039477362</v>
+        <v>0.9738237986275606</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>0</v>
@@ -8202,7 +8202,7 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.0320582122730573</v>
+        <v>-0.7165675357080536</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
@@ -8212,52 +8212,158 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
+        <v>4999</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>鑫禾</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>153.5185540640375</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>50.46720510913526</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>18.45052972271923</v>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>0.8622952530138016</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>0.0155610006807138</v>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>4942</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>嘉彰</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>121.2296432743812</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>44.10257854118134</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>14.25181969737796</v>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>1.143923039477362</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>-0.0320582123657867</v>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
         <v>5465</v>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>富驊</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D147" s="2" t="n">
-        <v>99.66755712267992</v>
-      </c>
-      <c r="E147" s="2" t="n">
+      <c r="C149" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>99.66755712268252</v>
+      </c>
+      <c r="E149" s="2" t="n">
         <v>25.5</v>
       </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>44.79866904331905</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>18.84239744523707</v>
-      </c>
-      <c r="J147" s="2" t="n">
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>44.79866920815921</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>18.84239741697861</v>
+      </c>
+      <c r="J149" s="2" t="n">
         <v>0.6381202325017881</v>
       </c>
-      <c r="K147" s="2" t="n">
+      <c r="K149" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M147" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N147" s="2" t="n">
-        <v>-0.149268433177583</v>
-      </c>
-      <c r="O147" s="2" t="inlineStr">
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>-0.1492684332497035</v>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
